--- a/kawasaki_project/05_試算・管理シート/川崎町_第9期_計画値実績対比表_R8.10.1.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_第9期_計画値実績対比表_R8.10.1.xlsx
@@ -8981,10 +8981,10 @@
         <v>353651</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>322680</v>
+        <v>322676</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>-30971</v>
+        <v>-30975</v>
       </c>
       <c r="E5" s="24" t="n">
         <v>91.2</v>
@@ -9005,10 +9005,10 @@
         <v>179884</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>182190</v>
+        <v>182194</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>2306</v>
+        <v>2310</v>
       </c>
       <c r="E6" s="24" t="n">
         <v>101.3</v>
@@ -9029,10 +9029,10 @@
         <v>477485</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>493350</v>
+        <v>493352</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>15865</v>
+        <v>15867</v>
       </c>
       <c r="E7" s="24" t="n">
         <v>103.3</v>
@@ -9053,10 +9053,10 @@
         <v>1011020</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>998220</v>
+        <v>998222</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>-12800</v>
+        <v>-12798</v>
       </c>
       <c r="E8" s="25" t="n">
         <v>98.7</v>
